--- a/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>JBT</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>444600</v>
+      </c>
+      <c r="E8" s="3">
         <v>403600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>427700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>388500</v>
       </c>
-      <c r="G8" s="3">
-        <v>599100</v>
-      </c>
       <c r="H8" s="3">
+        <v>441200</v>
+      </c>
+      <c r="I8" s="3">
         <v>398800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>394000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>356300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>497600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>477400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>475500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>417800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>439400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>419200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>411500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>457700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>545500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>489400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>493300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>417500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>537300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>481900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>491300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>409200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>483700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>420800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>386100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>344500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>405000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>349600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>281100</v>
+      </c>
+      <c r="E9" s="3">
         <v>259700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>281400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>256500</v>
       </c>
-      <c r="G9" s="3">
-        <v>432300</v>
-      </c>
       <c r="H9" s="3">
+        <v>295800</v>
+      </c>
+      <c r="I9" s="3">
         <v>263300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>265300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>236500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>356400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>334900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>325600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>284600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>306100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>292000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>281300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>311900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>379000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>340500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>337900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>289900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>379200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>346900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>351000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>305600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>346800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>299300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>270500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>247000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>969900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>255600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>163500</v>
+      </c>
+      <c r="E10" s="3">
         <v>143900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>146300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>132000</v>
       </c>
-      <c r="G10" s="3">
-        <v>166800</v>
-      </c>
       <c r="H10" s="3">
+        <v>145400</v>
+      </c>
+      <c r="I10" s="3">
         <v>135500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>128700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>119800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>141200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>142500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>149900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>133200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>133300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>127200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>130200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>145800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>166500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>148900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>155400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>127600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>158100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>135000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>140300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>103600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>136900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>121500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>115600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>97500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-564900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>94000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1160,38 +1173,41 @@
       <c r="V12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X12" s="3">
         <v>6200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,100 +1298,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E14" s="3">
         <v>6400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1000</v>
       </c>
       <c r="N14" s="3">
         <v>1000</v>
       </c>
       <c r="O14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2100</v>
-      </c>
-      <c r="R14" s="3">
-        <v>2000</v>
       </c>
       <c r="S14" s="3">
         <v>2000</v>
       </c>
       <c r="T14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>386800</v>
+      </c>
+      <c r="E17" s="3">
         <v>367600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>384300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>361000</v>
       </c>
-      <c r="G17" s="3">
-        <v>549400</v>
-      </c>
       <c r="H17" s="3">
+        <v>398400</v>
+      </c>
+      <c r="I17" s="3">
         <v>364000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>362000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>333300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>463100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>436900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>428200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>380000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>395900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>390900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>363900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>414000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>482900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>440800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>446300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>387500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>478200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>445300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>449100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>403300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>430300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>378600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>356400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>324000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>370700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>320100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E18" s="3">
         <v>36000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27500</v>
       </c>
-      <c r="G18" s="3">
-        <v>49700</v>
-      </c>
       <c r="H18" s="3">
+        <v>42800</v>
+      </c>
+      <c r="I18" s="3">
         <v>34800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>32000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>37800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>43700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>62600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>48600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>47000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>59100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>36600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>42200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>53400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>42200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>29700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>34300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,52 +1747,53 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-200</v>
       </c>
       <c r="F20" s="3">
         <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1000</v>
       </c>
       <c r="R20" s="3">
         <v>-1000</v>
@@ -1769,7 +1802,7 @@
         <v>-1000</v>
       </c>
       <c r="T20" s="3">
-        <v>-500</v>
+        <v>-1000</v>
       </c>
       <c r="U20" s="3">
         <v>-500</v>
@@ -1778,20 +1811,20 @@
         <v>-500</v>
       </c>
       <c r="W20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1802,134 +1835,140 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>92900</v>
+      </c>
+      <c r="E21" s="3">
         <v>58800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>65500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51200</v>
       </c>
-      <c r="G21" s="3">
-        <v>75500</v>
-      </c>
       <c r="H21" s="3">
+        <v>67400</v>
+      </c>
+      <c r="I21" s="3">
         <v>53500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>48700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>42900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>56100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>60400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>65600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>56100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>64300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>60200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>79700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>65300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>62100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>44200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>73400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>51900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>55900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>19400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>67200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>55000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>32700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>46200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6500</v>
       </c>
-      <c r="G22" s="3">
-        <v>6000</v>
-      </c>
       <c r="H22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I22" s="3">
         <v>3200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>2100</v>
       </c>
       <c r="M22" s="3">
         <v>2100</v>
@@ -1938,31 +1977,31 @@
         <v>2100</v>
       </c>
       <c r="O22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P22" s="3">
         <v>2700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3300</v>
-      </c>
-      <c r="W22" s="3">
-        <v>3400</v>
       </c>
       <c r="X22" s="3">
         <v>3400</v>
@@ -1971,212 +2010,221 @@
         <v>3400</v>
       </c>
       <c r="Z22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AA22" s="3">
         <v>3700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E23" s="3">
         <v>34800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>36100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20800</v>
       </c>
-      <c r="G23" s="3">
-        <v>43800</v>
-      </c>
       <c r="H23" s="3">
+        <v>37400</v>
+      </c>
+      <c r="I23" s="3">
         <v>31500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>35700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>40200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>43100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>37900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>56200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>42200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>42300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>26200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>55400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>33200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>38400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>50100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>38600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>26700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E24" s="3">
         <v>4300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4400</v>
       </c>
-      <c r="G24" s="3">
-        <v>6300</v>
-      </c>
       <c r="H24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I24" s="3">
         <v>5800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E26" s="3">
         <v>30500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16400</v>
       </c>
-      <c r="G26" s="3">
-        <v>37500</v>
-      </c>
       <c r="H26" s="3">
-        <v>25700</v>
+        <v>32500</v>
       </c>
       <c r="I26" s="3">
         <v>25700</v>
       </c>
       <c r="J26" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K26" s="3">
         <v>19900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>29300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>32500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>42100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>34000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>41800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>33500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>35300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>17600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E27" s="3">
         <v>30500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16400</v>
       </c>
-      <c r="G27" s="3">
-        <v>37500</v>
-      </c>
       <c r="H27" s="3">
-        <v>25700</v>
+        <v>32500</v>
       </c>
       <c r="I27" s="3">
         <v>25700</v>
       </c>
       <c r="J27" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K27" s="3">
         <v>19900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>29300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>32500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>42100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>34000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>41800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>33500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>17600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2543,35 +2600,38 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E29" s="3">
         <v>437100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>3300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>9200</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="H29" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I29" s="3">
         <v>8500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>7700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>5700</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2600,43 +2660,46 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-300</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>1100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-300</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2819,52 +2885,55 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>200</v>
       </c>
       <c r="F32" s="3">
         <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1000</v>
       </c>
       <c r="R32" s="3">
         <v>1000</v>
@@ -2873,7 +2942,7 @@
         <v>1000</v>
       </c>
       <c r="T32" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="U32" s="3">
         <v>500</v>
@@ -2882,20 +2951,20 @@
         <v>500</v>
       </c>
       <c r="W32" s="3">
+        <v>500</v>
+      </c>
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2906,105 +2975,111 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E33" s="3">
         <v>467600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25600</v>
       </c>
-      <c r="G33" s="3">
-        <v>37500</v>
-      </c>
       <c r="H33" s="3">
+        <v>44200</v>
+      </c>
+      <c r="I33" s="3">
         <v>34200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>33400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>29300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>32500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>42100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>33500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>33700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>42900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>33600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>19400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>25800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E35" s="3">
         <v>467600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25600</v>
       </c>
-      <c r="G35" s="3">
-        <v>37500</v>
-      </c>
       <c r="H35" s="3">
+        <v>44200</v>
+      </c>
+      <c r="I35" s="3">
         <v>34200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>33400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>29300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>32500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>42100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>33500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>33700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>42900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>33600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>19400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>25800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3352,108 +3437,112 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>483300</v>
+      </c>
+      <c r="E41" s="3">
         <v>401700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45700</v>
       </c>
-      <c r="G41" s="3">
-        <v>73100</v>
-      </c>
       <c r="H41" s="3">
+        <v>71700</v>
+      </c>
+      <c r="I41" s="3">
         <v>52600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>58200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>202300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>58000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>75400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>49100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>36300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>34000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>42900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E42" s="3">
         <v>125000</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>91</v>
@@ -3470,8 +3559,8 @@
       <c r="J42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3536,376 +3625,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>288900</v>
+      </c>
+      <c r="E43" s="3">
         <v>259900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>279600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>383800</v>
       </c>
-      <c r="G43" s="3">
-        <v>388600</v>
-      </c>
       <c r="H43" s="3">
+        <v>265600</v>
+      </c>
+      <c r="I43" s="3">
         <v>374100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>366600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>340900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>333500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>319700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>307100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>281500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>304400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>305000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>302600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>338700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>363300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>354700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>357300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>295800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>323700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>334000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>318700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>287600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>316400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>299900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>281800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>246600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>260500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>240900</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>238900</v>
+      </c>
+      <c r="E44" s="3">
         <v>226700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>237200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>351900</v>
       </c>
-      <c r="G44" s="3">
-        <v>322500</v>
-      </c>
       <c r="H44" s="3">
+        <v>202000</v>
+      </c>
+      <c r="I44" s="3">
         <v>346800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>298800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>275600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>229100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>217900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>204100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>195700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>197300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>219700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>229100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>237200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>245000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>264000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>260400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>226400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>206100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>256600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>270500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>305400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>190200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>217500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>198300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>178400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>139600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>89100</v>
+      </c>
+      <c r="E45" s="3">
         <v>78300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>327200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>84800</v>
       </c>
-      <c r="G45" s="3">
-        <v>85400</v>
-      </c>
       <c r="H45" s="3">
+        <v>325200</v>
+      </c>
+      <c r="I45" s="3">
         <v>100900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>73400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>76400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>77300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>68600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>64600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>62700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>66900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>59200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>50500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>51700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>60400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>57300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>58600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>60700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>45700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>57600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>59700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>55000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>48000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>53500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>54000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>52600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>51700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>40200</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1100200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1091600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>886800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>866200</v>
       </c>
-      <c r="G46" s="3">
-        <v>869600</v>
-      </c>
       <c r="H46" s="3">
+        <v>926500</v>
+      </c>
+      <c r="I46" s="3">
         <v>874400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>806900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>777100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>718700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>664400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>778100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>597400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>616100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>634500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>640200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>703000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>708200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>725100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>715400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>626800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>618500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>686700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>685200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>678600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>588600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>609300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>560400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>520500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>485000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E48" s="3">
         <v>245100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>246600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>273100</v>
       </c>
-      <c r="G48" s="3">
-        <v>269900</v>
-      </c>
       <c r="H48" s="3">
+        <v>245400</v>
+      </c>
+      <c r="I48" s="3">
         <v>262200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>263400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>269200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>267600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>268300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>267800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>263300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>268000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>261900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>262200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>261300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>265600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>264500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>265400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>237500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>239700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>238900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>234800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>242900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>233000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>231000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>220700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>216800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>210200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>187600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1168400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1166200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1186400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1249700</v>
       </c>
-      <c r="G49" s="3">
-        <v>1253200</v>
-      </c>
       <c r="H49" s="3">
+        <v>1200200</v>
+      </c>
+      <c r="I49" s="3">
         <v>1236000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>976600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1011000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1027400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>999400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>841300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>846600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>843000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>832900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>828000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>831200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>854800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>842800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>856600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>576500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>535300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>543000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>508900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>524100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>518600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>522300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>479900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>474900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>425500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>193800</v>
+      </c>
+      <c r="E52" s="3">
         <v>185900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>268000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>190600</v>
       </c>
-      <c r="G52" s="3">
-        <v>191400</v>
-      </c>
       <c r="H52" s="3">
+        <v>268900</v>
+      </c>
+      <c r="I52" s="3">
         <v>181900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>175200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>152600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>127700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>106400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>89100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>87000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>78800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>82600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>90600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>88700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>86300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>86400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>74900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>80800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>49000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>52600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>50200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>52400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>51200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>62300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>58600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>59600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>66700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2710400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2688800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2587800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2579600</v>
       </c>
-      <c r="G54" s="3">
-        <v>2584100</v>
-      </c>
       <c r="H54" s="3">
+        <v>2641000</v>
+      </c>
+      <c r="I54" s="3">
         <v>2554500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2222100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2209900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2141400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2038500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1976300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1794300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1805900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1811900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1821000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1884200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1914900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1918800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1912300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1521600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1442500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1521200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1479100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1498000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1391400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1424900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1319600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1271800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1187400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>960700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E57" s="3">
         <v>121300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>137400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>215300</v>
       </c>
-      <c r="G57" s="3">
-        <v>237000</v>
-      </c>
       <c r="H57" s="3">
+        <v>170600</v>
+      </c>
+      <c r="I57" s="3">
         <v>221000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>222900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>212500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>186000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>183400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>177900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>150000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>140700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>152000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>150400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>159200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>198600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>186800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>189100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>154800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>191200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>174100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>162100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>156800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>157100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>159100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>139400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>137300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>135700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>120700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -4809,459 +4942,474 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="J58" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2900</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>500</v>
-      </c>
-      <c r="X58" s="3">
-        <v>100</v>
       </c>
       <c r="Y58" s="3">
         <v>100</v>
       </c>
       <c r="Z58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA58" s="3">
         <v>8900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>349800</v>
+      </c>
+      <c r="E59" s="3">
         <v>463000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>471700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>402200</v>
       </c>
-      <c r="G59" s="3">
-        <v>383600</v>
-      </c>
       <c r="H59" s="3">
+        <v>452800</v>
+      </c>
+      <c r="I59" s="3">
         <v>397400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>383800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>383300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>363900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>319100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>318900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>314400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>282400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>261800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>252600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>275000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>284400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>292000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>298700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>293600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>322200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>353900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>378000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>273800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>304000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>256700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>257100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>250200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>484400</v>
+      </c>
+      <c r="E60" s="3">
         <v>584300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>610000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>618300</v>
       </c>
-      <c r="G60" s="3">
-        <v>621200</v>
-      </c>
       <c r="H60" s="3">
+        <v>624000</v>
+      </c>
+      <c r="I60" s="3">
         <v>619200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>606700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>595900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>549900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>502800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>478900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>469400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>457500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>434600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>412300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>412100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>474500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>472800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>484000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>453500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>485300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>496400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>516100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>543700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>441400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>475300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>403700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>402200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>393000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>390500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>646400</v>
+      </c>
+      <c r="E61" s="3">
         <v>645800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>949600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>956500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>977300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>979000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>674600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>669900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>674400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>652900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>641100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>469300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>522500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>598000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>647600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>733600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>698300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>768700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>771500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>448200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>387100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>486100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>437200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>407400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>372700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>391800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>391900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>372600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>491600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>300200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E62" s="3">
         <v>85600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>107000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>113800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>134300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>150100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>151000</v>
+      </c>
+      <c r="K62" s="3">
+        <v>160500</v>
+      </c>
+      <c r="L62" s="3">
+        <v>166600</v>
+      </c>
+      <c r="M62" s="3">
+        <v>175500</v>
+      </c>
+      <c r="N62" s="3">
+        <v>170600</v>
+      </c>
+      <c r="O62" s="3">
+        <v>183500</v>
+      </c>
+      <c r="P62" s="3">
+        <v>188800</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>167900</v>
+      </c>
+      <c r="R62" s="3">
+        <v>164500</v>
+      </c>
+      <c r="S62" s="3">
+        <v>167800</v>
+      </c>
+      <c r="T62" s="3">
+        <v>172600</v>
+      </c>
+      <c r="U62" s="3">
+        <v>153600</v>
+      </c>
+      <c r="V62" s="3">
+        <v>156800</v>
+      </c>
+      <c r="W62" s="3">
+        <v>143500</v>
+      </c>
+      <c r="X62" s="3">
+        <v>113200</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>106300</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>115200</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>127900</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>135400</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>127500</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>121300</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>120700</v>
+      </c>
+      <c r="AF62" s="3">
         <v>122900</v>
       </c>
-      <c r="H62" s="3">
-        <v>150100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>151000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>160500</v>
-      </c>
-      <c r="K62" s="3">
-        <v>166600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>175500</v>
-      </c>
-      <c r="M62" s="3">
-        <v>170600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>183500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>188800</v>
-      </c>
-      <c r="P62" s="3">
-        <v>167900</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>164500</v>
-      </c>
-      <c r="R62" s="3">
-        <v>167800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>172600</v>
-      </c>
-      <c r="T62" s="3">
-        <v>153600</v>
-      </c>
-      <c r="U62" s="3">
-        <v>156800</v>
-      </c>
-      <c r="V62" s="3">
-        <v>143500</v>
-      </c>
-      <c r="W62" s="3">
-        <v>113200</v>
-      </c>
-      <c r="X62" s="3">
-        <v>106300</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>115200</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>127900</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>135400</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>127500</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>121300</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>120700</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>122900</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1221500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1315700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1666600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1688600</v>
       </c>
-      <c r="G66" s="3">
-        <v>1721400</v>
-      </c>
       <c r="H66" s="3">
+        <v>1735600</v>
+      </c>
+      <c r="I66" s="3">
         <v>1748300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1432300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1426300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1390900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1331200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1290600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1122200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1168800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1200500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1224400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1313500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1345400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1395100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1412300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1045200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>985600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1088800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1068500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1079000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>949500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>994600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>916900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>895500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1007500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>791600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1463600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1365600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>901500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>873700</v>
       </c>
-      <c r="G72" s="3">
-        <v>851300</v>
-      </c>
       <c r="H72" s="3">
+        <v>894000</v>
+      </c>
+      <c r="I72" s="3">
         <v>817000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>786000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>755800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>733400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>705000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>678900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>651600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>627800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>600900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>586900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>557600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>532800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>493900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>463700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>433100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>416500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>354700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>333800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>303400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>333700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>317600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>295000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>280300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>266600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1488900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1373100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>921200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>891000</v>
       </c>
-      <c r="G76" s="3">
-        <v>862700</v>
-      </c>
       <c r="H76" s="3">
+        <v>905400</v>
+      </c>
+      <c r="I76" s="3">
         <v>806200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>789800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>783600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>750500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>707300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>685700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>672100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>637100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>611400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>596600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>570700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>569500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>523700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>500000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>476400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>456900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>432400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>410600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>419000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>441900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>430300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>402700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>376300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>179900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E81" s="3">
         <v>467600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25600</v>
       </c>
-      <c r="G81" s="3">
-        <v>37500</v>
-      </c>
       <c r="H81" s="3">
+        <v>44200</v>
+      </c>
+      <c r="I81" s="3">
         <v>34200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>33400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>29300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>32500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>42100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>33500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>33700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>42900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>33600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>19400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>25800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E83" s="3">
         <v>23100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>18300</v>
       </c>
       <c r="N83" s="3">
         <v>18300</v>
       </c>
       <c r="O83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="P83" s="3">
         <v>18600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E89" s="3">
         <v>16300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>26300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>67700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>62400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>85700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>90900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>60100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>87200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>75300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>127900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>19200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>36600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>66600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>23800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>40600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-24300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-20600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8300</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-10400</v>
       </c>
       <c r="AA91" s="3">
         <v>-10400</v>
       </c>
       <c r="AB91" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E94" s="3">
         <v>647600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-349600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-55700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-182700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-330100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-68400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-240600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -7885,55 +8117,56 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-3200</v>
       </c>
       <c r="F96" s="3">
         <v>-3200</v>
       </c>
       <c r="G96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="H96" s="3">
         <v>-3300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-3200</v>
       </c>
       <c r="S96" s="3">
         <v>-3200</v>
@@ -7942,28 +8175,28 @@
         <v>-3200</v>
       </c>
       <c r="U96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AC96" s="3">
         <v>-3200</v>
@@ -7972,13 +8205,16 @@
         <v>-3200</v>
       </c>
       <c r="AE96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="AF96" s="3">
         <v>-2900</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-2900</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8253,156 +8495,162 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-304900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-28000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>307900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>109800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-50000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-86100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-61100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-94500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>34300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-81000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>314000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>53700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-113500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>39300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>29900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>15500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>53500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>186900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-2900</v>
       </c>
       <c r="I101" s="3">
         <v>-2900</v>
       </c>
       <c r="J101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>200</v>
       </c>
       <c r="V101" s="3">
         <v>200</v>
@@ -8411,122 +8659,128 @@
         <v>200</v>
       </c>
       <c r="X101" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E102" s="3">
         <v>357000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-144100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>144800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>35900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-16600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>JBT</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>392300</v>
+      </c>
+      <c r="E8" s="3">
         <v>444600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>403600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>427700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>388500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>441200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>398800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>394000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>356300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>497600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>477400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>475500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>417800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>439400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>419200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>411500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>457700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>545500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>489400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>493300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>417500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>537300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>481900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>491300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>409200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>483700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>420800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>386100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>344500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>405000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>349600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E9" s="3">
         <v>281100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>259700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>281400</v>
       </c>
-      <c r="G9" s="3">
-        <v>256500</v>
-      </c>
       <c r="H9" s="3">
+        <v>512100</v>
+      </c>
+      <c r="I9" s="3">
         <v>295800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>263300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>265300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>236500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>356400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>334900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>325600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>284600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>306100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>292000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>281300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>311900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>379000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>340500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>337900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>289900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>379200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>346900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>351000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>305600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>346800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>299300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>270500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>247000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>969900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>255600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>140300</v>
+      </c>
+      <c r="E10" s="3">
         <v>163500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>143900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>146300</v>
       </c>
-      <c r="G10" s="3">
-        <v>132000</v>
-      </c>
       <c r="H10" s="3">
+        <v>-123600</v>
+      </c>
+      <c r="I10" s="3">
         <v>145400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>135500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>128700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>119800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>141200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>142500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>149900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>133200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>133300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>127200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>130200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>145800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>166500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>148900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>155400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>127600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>158100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>135000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>140300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>103600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>136900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>121500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>115600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>97500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-564900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>94000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1176,38 +1190,41 @@
       <c r="W12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y12" s="3">
         <v>6200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,103 +1318,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1000</v>
       </c>
       <c r="O14" s="3">
         <v>1000</v>
       </c>
       <c r="P14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2100</v>
-      </c>
-      <c r="S14" s="3">
-        <v>2000</v>
       </c>
       <c r="T14" s="3">
         <v>2000</v>
       </c>
       <c r="U14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>363200</v>
+      </c>
+      <c r="E17" s="3">
         <v>386800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>367600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>384300</v>
       </c>
-      <c r="G17" s="3">
-        <v>361000</v>
-      </c>
       <c r="H17" s="3">
+        <v>360100</v>
+      </c>
+      <c r="I17" s="3">
         <v>398400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>364000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>362000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>333300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>463100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>436900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>428200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>380000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>395900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>390900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>363900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>414000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>482900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>440800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>446300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>387500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>478200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>445300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>449100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>403300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>430300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>378600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>356400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>324000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>370700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>320100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E18" s="3">
         <v>57800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>36000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>43400</v>
       </c>
-      <c r="G18" s="3">
-        <v>27500</v>
-      </c>
       <c r="H18" s="3">
+        <v>28400</v>
+      </c>
+      <c r="I18" s="3">
         <v>42800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>40500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>47600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>62600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>48600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>47000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>59100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>36600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>42200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>53400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>42200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>29700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>34300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1748,55 +1781,56 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>13100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-200</v>
       </c>
       <c r="G20" s="3">
         <v>-200</v>
       </c>
       <c r="H20" s="3">
+        <v>800</v>
+      </c>
+      <c r="I20" s="3">
         <v>3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-1000</v>
       </c>
       <c r="S20" s="3">
         <v>-1000</v>
@@ -1805,7 +1839,7 @@
         <v>-1000</v>
       </c>
       <c r="U20" s="3">
-        <v>-500</v>
+        <v>-1000</v>
       </c>
       <c r="V20" s="3">
         <v>-500</v>
@@ -1814,20 +1848,20 @@
         <v>-500</v>
       </c>
       <c r="X20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1838,140 +1872,146 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E21" s="3">
         <v>92900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>58800</v>
       </c>
-      <c r="F21" s="3">
-        <v>65500</v>
-      </c>
       <c r="G21" s="3">
-        <v>51200</v>
+        <v>66700</v>
       </c>
       <c r="H21" s="3">
+        <v>51900</v>
+      </c>
+      <c r="I21" s="3">
         <v>67400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>56100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>60400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>65600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>56100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>64300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>60200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>79700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>65300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>62100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>44200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>73400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>51900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>55900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>19400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>67200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>55000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>32700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>46200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>9800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7100</v>
       </c>
-      <c r="G22" s="3">
-        <v>6500</v>
-      </c>
       <c r="H22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I22" s="3">
         <v>9200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>2100</v>
       </c>
       <c r="N22" s="3">
         <v>2100</v>
@@ -1980,31 +2020,31 @@
         <v>2100</v>
       </c>
       <c r="P22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>2700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3300</v>
-      </c>
-      <c r="X22" s="3">
-        <v>3400</v>
       </c>
       <c r="Y22" s="3">
         <v>3400</v>
@@ -2013,218 +2053,227 @@
         <v>3400</v>
       </c>
       <c r="AA22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>3700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E23" s="3">
         <v>61100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36100</v>
       </c>
-      <c r="G23" s="3">
-        <v>20800</v>
-      </c>
       <c r="H23" s="3">
+        <v>21700</v>
+      </c>
+      <c r="I23" s="3">
         <v>37400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>38300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>35700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>40200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>43100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>37900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>56200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>42200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>42300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>26200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>55400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>33200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>50100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>38600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>26400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>31900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>26700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E24" s="3">
         <v>6400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8400</v>
       </c>
-      <c r="G24" s="3">
-        <v>4400</v>
-      </c>
       <c r="H24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I24" s="3">
         <v>4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>14800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E26" s="3">
         <v>54700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27700</v>
       </c>
-      <c r="G26" s="3">
-        <v>16400</v>
-      </c>
       <c r="H26" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I26" s="3">
         <v>32500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>25700</v>
       </c>
       <c r="J26" s="3">
         <v>25700</v>
       </c>
       <c r="K26" s="3">
+        <v>25700</v>
+      </c>
+      <c r="L26" s="3">
         <v>19900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>31600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>29300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>32500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>29000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>42100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>34000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>41800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>33500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>35300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E27" s="3">
         <v>54700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27700</v>
       </c>
-      <c r="G27" s="3">
-        <v>16400</v>
-      </c>
       <c r="H27" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I27" s="3">
         <v>32500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>25700</v>
       </c>
       <c r="J27" s="3">
         <v>25700</v>
       </c>
       <c r="K27" s="3">
+        <v>25700</v>
+      </c>
+      <c r="L27" s="3">
         <v>19900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>29300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>29000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>42100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>33500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>41800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>33500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2603,38 +2661,41 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>100</v>
+      </c>
+      <c r="E29" s="3">
         <v>3700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>437100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>3300</v>
       </c>
-      <c r="G29" s="3">
-        <v>9200</v>
-      </c>
       <c r="H29" s="3">
+        <v>19300</v>
+      </c>
+      <c r="I29" s="3">
         <v>11700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>8500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>7700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>5700</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2663,43 +2724,46 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-300</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>1100</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-15900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-300</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2888,55 +2955,58 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>200</v>
       </c>
       <c r="G32" s="3">
         <v>200</v>
       </c>
       <c r="H32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>1000</v>
       </c>
       <c r="S32" s="3">
         <v>1000</v>
@@ -2945,7 +3015,7 @@
         <v>1000</v>
       </c>
       <c r="U32" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="V32" s="3">
         <v>500</v>
@@ -2954,20 +3024,20 @@
         <v>500</v>
       </c>
       <c r="X32" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2978,108 +3048,114 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E33" s="3">
         <v>58400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>467600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>36400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>44200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K33" s="3">
+        <v>33400</v>
+      </c>
+      <c r="L33" s="3">
         <v>25600</v>
       </c>
-      <c r="H33" s="3">
-        <v>44200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>34200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>33400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>25600</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>31600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>29300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>29000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>42100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>33500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>42900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>33600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>25800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E35" s="3">
         <v>58400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>467600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>36400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>44200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K35" s="3">
+        <v>33400</v>
+      </c>
+      <c r="L35" s="3">
         <v>25600</v>
       </c>
-      <c r="H35" s="3">
-        <v>44200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>34200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>33400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>25600</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>31600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>29300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>29000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>42100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>33500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>42900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>33600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>25800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3438,114 +3524,118 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E41" s="3">
         <v>483300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>401700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>45700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>68100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>58200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>202300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>57500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>58000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>75400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>36300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>34000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>38400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>26300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>42900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>33200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F42" s="3">
         <v>125000</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>91</v>
@@ -3562,8 +3652,8 @@
       <c r="K42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3628,388 +3718,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>299300</v>
+      </c>
+      <c r="E43" s="3">
         <v>288900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>259900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>279600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>383800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>265600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>374100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>366600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>340900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>333500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>319700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>307100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>281500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>304400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>305000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>302600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>338700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>363300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>354700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>357300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>295800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>323700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>334000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>318700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>287600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>316400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>299900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>281800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>246600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>260500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>240900</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E44" s="3">
         <v>238900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>226700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>237200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>351900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>202000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>346800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>298800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>275600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>229100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>217900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>204100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>195700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>197300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>219700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>229100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>237200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>245000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>264000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>260400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>226400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>206100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>256600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>270500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>305400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>190200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>217500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>198300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>178400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>139600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E45" s="3">
         <v>89100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>78300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>327200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>84800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>325200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>73400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>76400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>77300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>68600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>64600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>62700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>66900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>59200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>50500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>51700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>60400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>57300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>58600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>60700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>57600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>59700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>55000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>53500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>54000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>51700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>40200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1102400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1100200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1091600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>886800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>866200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>926500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>874400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>806900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>777100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>718700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>664400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>778100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>597400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>616100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>634500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>640200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>703000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>708200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>725100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>715400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>626800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>618500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>686700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>685200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>678600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>588600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>609300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>560400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>520500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>485000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>246700</v>
+      </c>
+      <c r="E48" s="3">
         <v>248000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>245100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>246600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>273100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>245400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>262200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>263400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>269200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>267600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>268300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>267800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>263300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>268000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>261900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>262200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>261300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>265600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>264500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>265400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>237500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>239700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>238900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>234800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>242900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>233000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>231000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>220700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>216800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>210200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>187600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1151200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1168400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1166200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1186400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1249700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1200200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1236000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>976600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1011000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1027400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>999400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>841300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>846600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>843000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>832900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>828000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>831200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>854800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>842800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>856600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>576500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>535300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>543000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>508900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>524100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>518600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>522300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>479900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>474900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>425500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>190400</v>
+      </c>
+      <c r="E52" s="3">
         <v>193800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>185900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>268000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>190600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>268900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>181900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>175200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>152600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>127700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>106400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>89100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>87000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>78800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>82600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>90600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>88700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>86300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>86400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>74900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>80800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>49000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>52600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>50200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>52400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>51200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>62300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>58600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>59600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>66700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2690700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2710400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2688800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2587800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2579600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2641000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2554500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2222100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2209900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2141400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2038500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1976300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1794300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1805900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1811900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1821000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1884200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1914900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1918800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1912300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1521600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1442500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1521200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1479100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1498000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1391400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1424900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1319600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1271800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1187400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>960700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E57" s="3">
         <v>134600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>121300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>137400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>215300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>170600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>221000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>222900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>212500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>186000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>183400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>177900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>150000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>140700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>152000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>150400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>159200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>198600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>186800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>189100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>154800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>191200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>174100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>162100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>156800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>157100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>159100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>139400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>137300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>135700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>120700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="K58" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2900</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>500</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>100</v>
       </c>
       <c r="Z58" s="3">
         <v>100</v>
       </c>
       <c r="AA58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB58" s="3">
         <v>8900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>323700</v>
+      </c>
+      <c r="E59" s="3">
         <v>349800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>463000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>471700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>402200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>452800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>397400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>383800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>383300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>363900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>319100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>318900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>314400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>282400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>261800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>252600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>275000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>284400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>292000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>298700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>293600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>322200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>353900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>378000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>273800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>304000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>256700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>257100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>250200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>466100</v>
+      </c>
+      <c r="E60" s="3">
         <v>484400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>584300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>610000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>618300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>624000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>619200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>606700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>595900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>549900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>502800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>478900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>469400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>457500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>434600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>412300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>412100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>474500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>472800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>484000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>453500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>485300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>496400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>516100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>543700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>441400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>475300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>403700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>402200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>393000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>390500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E61" s="3">
         <v>646400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>645800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>949600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>956500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>977300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>979000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>674600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>669900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>674400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>652900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>641100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>469300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>522500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>598000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>647600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>733600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>698300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>768700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>771500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>448200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>387100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>486100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>437200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>407400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>372700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>391800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>391900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>372600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>491600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>300200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E62" s="3">
         <v>90700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>85600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>107000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>113800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>134300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>150100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>151000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>160500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>166600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>175500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>170600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>183500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>188800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>167900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>164500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>167800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>172600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>153600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>156800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>143500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>113200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>106300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>115200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>127900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>135400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>127500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>121300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>120700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>122900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1199600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1221500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1315700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1666600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1688600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1735600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1748300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1432300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1426300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1390900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1331200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1290600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1122200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1168800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1200500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1224400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1313500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1345400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1395100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1412300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1045200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>985600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1088800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1068500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1079000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>949500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>994600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>916900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>895500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1007500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>791600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1483100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1463600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1365600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>901500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>873700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>894000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>817000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>786000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>755800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>733400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>705000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>678900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>651600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>627800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>600900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>586900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>557600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>532800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>493900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>463700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>433100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>416500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>354700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>333800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>303400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>333700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>317600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>295000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>280300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>266600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1491100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1488900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1373100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>921200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>891000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>905400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>806200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>789800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>783600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>750500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>707300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>685700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>672100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>637100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>611400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>596600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>570700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>569500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>523700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>500000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>476400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>456900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>432400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>410600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>419000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>441900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>430300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>402700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>376300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>179900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E81" s="3">
         <v>58400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>467600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>36400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>44200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K81" s="3">
+        <v>33400</v>
+      </c>
+      <c r="L81" s="3">
         <v>25600</v>
       </c>
-      <c r="H81" s="3">
-        <v>44200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>34200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>33400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>25600</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>31600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>29300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>29000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>42100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>33500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>42900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>33600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>25800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>18300</v>
       </c>
       <c r="O83" s="3">
         <v>18300</v>
       </c>
       <c r="P83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>18600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>18100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>15600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>14600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>26300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>67700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>62400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>85700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>90900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>60100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>87200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>75300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>127900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>19200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>36600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>66600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>23800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10900</v>
       </c>
-      <c r="F91" s="3">
-        <v>-17400</v>
-      </c>
       <c r="G91" s="3">
-        <v>-17900</v>
+        <v>-19000</v>
       </c>
       <c r="H91" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-21300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8300</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-10400</v>
       </c>
       <c r="AB91" s="3">
         <v>-10400</v>
       </c>
       <c r="AC91" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E94" s="3">
         <v>113200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>647600</v>
       </c>
-      <c r="F94" s="3">
-        <v>-16000</v>
-      </c>
       <c r="G94" s="3">
-        <v>-18900</v>
+        <v>-17600</v>
       </c>
       <c r="H94" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-24000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-349600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-55700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-182700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-330100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-54900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-50700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-68400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-240600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8118,58 +8351,59 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-3200</v>
       </c>
       <c r="G96" s="3">
         <v>-3200</v>
       </c>
       <c r="H96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I96" s="3">
         <v>-3300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-3200</v>
       </c>
       <c r="T96" s="3">
         <v>-3200</v>
@@ -8178,28 +8412,28 @@
         <v>-3200</v>
       </c>
       <c r="V96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="W96" s="3">
         <v>-3100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AD96" s="3">
         <v>-3200</v>
@@ -8208,13 +8442,16 @@
         <v>-3200</v>
       </c>
       <c r="AF96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="AG96" s="3">
         <v>-2900</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-2900</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8498,162 +8741,168 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-304900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>307900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>109800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-50000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-86100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-61100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-94500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>34300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-81000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>314000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>53700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-113500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>39300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>29900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>53500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>186900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-2900</v>
       </c>
       <c r="J101" s="3">
         <v>-2900</v>
       </c>
       <c r="K101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>200</v>
       </c>
       <c r="W101" s="3">
         <v>200</v>
@@ -8662,125 +8911,131 @@
         <v>200</v>
       </c>
       <c r="Y101" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>81600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>357000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-144100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>144800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>35900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>JBT</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>402300</v>
+      </c>
+      <c r="E8" s="3">
         <v>392300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>444600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>403600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>427700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>388500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>441200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>398800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>394000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>356300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>497600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>477400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>475500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>417800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>439400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>419200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>411500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>457700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>545500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>489400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>493300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>417500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>537300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>481900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>491300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>409200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>483700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>420800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>386100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>344500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>405000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>349600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>259100</v>
+      </c>
+      <c r="E9" s="3">
         <v>252000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>281100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>259700</v>
       </c>
-      <c r="G9" s="3">
-        <v>281400</v>
-      </c>
       <c r="H9" s="3">
+        <v>304900</v>
+      </c>
+      <c r="I9" s="3">
         <v>512100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>295800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>263300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>265300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>236500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>356400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>334900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>325600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>284600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>306100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>292000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>281300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>311900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>379000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>340500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>337900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>289900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>379200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>346900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>351000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>305600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>346800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>299300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>270500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>247000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>969900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>255600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E10" s="3">
         <v>140300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>163500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>143900</v>
       </c>
-      <c r="G10" s="3">
-        <v>146300</v>
-      </c>
       <c r="H10" s="3">
+        <v>122800</v>
+      </c>
+      <c r="I10" s="3">
         <v>-123600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>145400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>135500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>128700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>119800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>141200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>142500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>149900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>133200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>133300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>127200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>130200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>145800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>166500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>148900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>155400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>127600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>158100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>135000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>140300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>103600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>136900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>121500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>115600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>97500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-564900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>94000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1193,38 +1207,41 @@
       <c r="X12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z12" s="3">
         <v>6200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,106 +1338,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1000</v>
       </c>
       <c r="P14" s="3">
         <v>1000</v>
       </c>
       <c r="Q14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>2000</v>
       </c>
       <c r="U14" s="3">
         <v>2000</v>
       </c>
       <c r="V14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>11600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>375500</v>
+      </c>
+      <c r="E17" s="3">
         <v>363200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>386800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>367600</v>
       </c>
-      <c r="G17" s="3">
-        <v>384300</v>
-      </c>
       <c r="H17" s="3">
+        <v>383400</v>
+      </c>
+      <c r="I17" s="3">
         <v>360100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>398400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>364000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>362000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>333300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>463100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>436900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>428200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>380000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>395900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>390900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>363900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>414000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>482900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>440800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>446300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>387500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>478200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>445300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>449100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>403300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>430300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>378600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>356400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>324000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>370700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>320100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E18" s="3">
         <v>29100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>36000</v>
       </c>
-      <c r="G18" s="3">
-        <v>43400</v>
-      </c>
       <c r="H18" s="3">
+        <v>44300</v>
+      </c>
+      <c r="I18" s="3">
         <v>28400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>42800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>43500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>28300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>62600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>48600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>47000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>30000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>59100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>36600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>42200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>53400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>42200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>29700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>34300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1791,49 +1825,49 @@
         <v>4700</v>
       </c>
       <c r="E20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F20" s="3">
         <v>13100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-200</v>
-      </c>
       <c r="H20" s="3">
+        <v>900</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1000</v>
       </c>
       <c r="T20" s="3">
         <v>-1000</v>
@@ -1842,7 +1876,7 @@
         <v>-1000</v>
       </c>
       <c r="V20" s="3">
-        <v>-500</v>
+        <v>-1000</v>
       </c>
       <c r="W20" s="3">
         <v>-500</v>
@@ -1851,20 +1885,20 @@
         <v>-500</v>
       </c>
       <c r="Y20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1875,146 +1909,152 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E21" s="3">
         <v>55900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>92900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>58800</v>
       </c>
-      <c r="G21" s="3">
-        <v>66700</v>
-      </c>
       <c r="H21" s="3">
+        <v>68700</v>
+      </c>
+      <c r="I21" s="3">
         <v>51900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>67400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>53500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>60400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>65600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>56100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>64300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>60200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>79700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>65300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>62100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>44200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>73400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>51900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>55900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>19400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>67200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>55000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>32700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>46200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E22" s="3">
         <v>2900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
-        <v>7100</v>
-      </c>
       <c r="H22" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I22" s="3">
         <v>7500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>2100</v>
       </c>
       <c r="O22" s="3">
         <v>2100</v>
@@ -2023,31 +2063,31 @@
         <v>2100</v>
       </c>
       <c r="Q22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R22" s="3">
         <v>2700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3300</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>3400</v>
       </c>
       <c r="Z22" s="3">
         <v>3400</v>
@@ -2056,224 +2096,233 @@
         <v>3400</v>
       </c>
       <c r="AB22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AC22" s="3">
         <v>3700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E23" s="3">
         <v>30900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>61100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34800</v>
       </c>
-      <c r="G23" s="3">
-        <v>36100</v>
-      </c>
       <c r="H23" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I23" s="3">
         <v>21700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>35700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>40200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>43100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>37900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>56200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>42200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>42300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>55400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>33200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>50100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>38600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>26400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>31900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>26700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4300</v>
       </c>
-      <c r="G24" s="3">
-        <v>8400</v>
-      </c>
       <c r="H24" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I24" s="3">
         <v>4600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>14800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E26" s="3">
         <v>22800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>54700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30500</v>
       </c>
-      <c r="G26" s="3">
-        <v>27700</v>
-      </c>
       <c r="H26" s="3">
+        <v>28400</v>
+      </c>
+      <c r="I26" s="3">
         <v>17100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>25700</v>
       </c>
       <c r="K26" s="3">
         <v>25700</v>
       </c>
       <c r="L26" s="3">
+        <v>25700</v>
+      </c>
+      <c r="M26" s="3">
         <v>19900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>31600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>32500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>33500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>34000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>41800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>33500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>35300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>26400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>23400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E27" s="3">
         <v>22700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>54700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30500</v>
       </c>
-      <c r="G27" s="3">
-        <v>27700</v>
-      </c>
       <c r="H27" s="3">
+        <v>28400</v>
+      </c>
+      <c r="I27" s="3">
         <v>17100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>25700</v>
       </c>
       <c r="K27" s="3">
         <v>25700</v>
       </c>
       <c r="L27" s="3">
+        <v>25700</v>
+      </c>
+      <c r="M27" s="3">
         <v>19900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>31600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>32500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>29000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>33500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>34000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>41800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>33500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>35300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>26400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>23400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,41 +2722,44 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>3700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>437100</v>
       </c>
-      <c r="G29" s="3">
-        <v>3300</v>
-      </c>
       <c r="H29" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I29" s="3">
         <v>19300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>11700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>8500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>7700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>5700</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2727,43 +2788,46 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-300</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-15900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-300</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -2967,49 +3037,49 @@
         <v>-4700</v>
       </c>
       <c r="E32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-13100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
-        <v>200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1000</v>
       </c>
       <c r="T32" s="3">
         <v>1000</v>
@@ -3018,7 +3088,7 @@
         <v>1000</v>
       </c>
       <c r="V32" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="W32" s="3">
         <v>500</v>
@@ -3027,20 +3097,20 @@
         <v>500</v>
       </c>
       <c r="Y32" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3051,111 +3121,117 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E33" s="3">
         <v>22800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>58400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>467600</v>
       </c>
-      <c r="G33" s="3">
-        <v>31000</v>
-      </c>
       <c r="H33" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I33" s="3">
         <v>36400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>44200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>31600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>32500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>29000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>33700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>42900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>33600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>25800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E35" s="3">
         <v>22800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>58400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>467600</v>
       </c>
-      <c r="G35" s="3">
-        <v>31000</v>
-      </c>
       <c r="H35" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I35" s="3">
         <v>36400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>44200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>31600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>32500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>29000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>33700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>42900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>33600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>25800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>474300</v>
+      </c>
+      <c r="E41" s="3">
         <v>479000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>483300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>401700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>45700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>78800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>58200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>202300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>47500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>58000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>75400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>49100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>39100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>36300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>26300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>42900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>33200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3634,11 +3724,11 @@
       <c r="E42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G42" s="3">
         <v>125000</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>91</v>
@@ -3655,8 +3745,8 @@
       <c r="L42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -3721,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>311500</v>
+      </c>
+      <c r="E43" s="3">
         <v>299300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>288900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>259900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>279600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>383800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>265600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>374100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>366600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>340900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>333500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>319700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>307100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>281500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>304400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>305000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>302600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>338700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>363300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>354700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>357300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>295800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>323700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>334000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>318700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>287600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>316400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>299900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>281800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>246600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>260500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>240900</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>258700</v>
+      </c>
+      <c r="E44" s="3">
         <v>250200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>238900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>226700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>237200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>351900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>202000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>346800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>298800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>275600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>229100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>217900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>204100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>195700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>197300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>219700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>229100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>237200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>245000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>264000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>260400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>226400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>206100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>256600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>270500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>305400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>190200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>217500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>198300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>178400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>139600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E45" s="3">
         <v>73900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>89100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>78300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>327200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>84800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>325200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>73400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>76400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>77300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>68600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>64600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>62700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>66900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>59200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>50500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>60400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>57300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>58600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>60700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>45700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>57600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>59700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>55000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>48000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>53500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>54000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>52600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>51700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>40200</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1125400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1102400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1100200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1091600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>886800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>866200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>926500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>874400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>806900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>777100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>718700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>664400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>778100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>597400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>616100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>634500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>640200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>703000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>708200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>725100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>715400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>626800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>618500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>686700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>685200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>678600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>588600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>609300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>560400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>520500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>485000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E48" s="3">
         <v>246700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>248000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>245100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>246600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>273100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>245400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>262200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>263400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>269200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>267600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>268300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>267800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>263300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>268000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>261900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>262200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>261300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>265600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>264500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>265400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>237500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>239700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>238900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>234800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>242900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>233000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>231000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>220700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>216800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>210200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>187600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1139000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1151200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1168400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1166200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1186400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1249700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1200200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1236000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>976600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1011000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1027400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>999400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>841300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>846600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>843000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>832900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>828000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>831200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>854800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>842800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>856600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>576500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>535300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>543000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>508900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>524100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>518600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>522300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>479900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>474900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>425500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>183700</v>
+      </c>
+      <c r="E52" s="3">
         <v>190400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>193800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>185900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>268000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>190600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>268900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>181900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>175200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>152600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>127700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>106400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>89100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>87000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>78800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>82600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>90600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>88700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>86300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>86400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>74900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>80800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>49000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>52600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>50200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>52400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>51200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>62300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>58600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>59600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>66700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2690100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2690700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2710400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2688800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2587800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2579600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2641000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2554500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2222100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2209900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2141400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2038500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1976300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1794300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1805900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1811900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1821000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1884200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1914900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1918800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1912300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1521600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1442500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1521200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1479100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1498000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1391400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1424900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1319600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1271800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1187400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>960700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>135600</v>
+      </c>
+      <c r="E57" s="3">
         <v>142400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>134600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>121300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>137400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>215300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>170600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>221000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>222900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>212500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>186000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>183400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>177900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>150000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>140700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>152000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>150400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>159200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>198600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>186800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>189100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>154800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>191200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>174100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>162100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>156800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>157100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>159100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>139400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>137300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>135700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>120700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2900</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>500</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>100</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
       </c>
       <c r="AB58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC58" s="3">
         <v>8900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>307300</v>
+      </c>
+      <c r="E59" s="3">
         <v>323700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>349800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>463000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>471700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>402200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>452800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>397400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>383800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>383300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>363900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>319100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>318900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>314400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>282400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>261800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>252600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>275000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>284400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>292000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>298700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>293600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>322200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>353900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>378000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>273800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>304000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>256700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>257100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>250200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>442900</v>
+      </c>
+      <c r="E60" s="3">
         <v>466100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>484400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>584300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>610000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>618300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>624000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>619200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>606700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>595900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>549900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>502800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>478900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>469400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>457500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>434600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>412300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>412100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>474500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>472800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>484000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>453500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>485300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>496400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>516100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>543700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>441400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>475300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>403700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>402200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>393000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>390500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>647600</v>
+      </c>
+      <c r="E61" s="3">
         <v>647000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>646400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>645800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>949600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>956500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>977300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>979000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>674600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>669900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>674400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>652900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>641100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>469300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>522500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>598000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>647600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>733600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>698300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>768700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>771500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>448200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>387100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>486100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>437200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>407400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>372700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>391800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>391900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>372600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>491600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>300200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E62" s="3">
         <v>86500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>90700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>85600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>107000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>113800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>134300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>150100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>160500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>166600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>175500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>170600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>183500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>188800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>167900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>164500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>167800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>172600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>153600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>156800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>143500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>113200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>106300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>115200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>127900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>135400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>127500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>121300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>120700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>122900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1171300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1199600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1221500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1315700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1666600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1688600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1735600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1748300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1432300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1426300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1390900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1331200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1290600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1122200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1168800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1200500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1224400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1313500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1345400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1395100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1412300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1045200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>985600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1088800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1068500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1079000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>949500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>994600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>916900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>895500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1007500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>791600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1510600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1483100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1463600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1365600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>901500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>873700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>894000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>817000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>786000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>755800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>733400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>705000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>678900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>651600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>627800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>600900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>586900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>557600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>532800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>493900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>463700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>433100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>416500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>354700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>333800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>303400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>333700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>317600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>295000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>280300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>266600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1518800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1491100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1488900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1373100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>921200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>891000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>905400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>806200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>789800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>783600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>750500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>707300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>685700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>672100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>637100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>611400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>596600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>570700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>569500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>523700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>500000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>476400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>456900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>432400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>410600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>419000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>441900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>430300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>402700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>376300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>179900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E81" s="3">
         <v>22800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>58400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>467600</v>
       </c>
-      <c r="G81" s="3">
-        <v>31000</v>
-      </c>
       <c r="H81" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I81" s="3">
         <v>36400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>44200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>31600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>32500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>29000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>33700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>42900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>33600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>25800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E83" s="3">
         <v>22100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>18300</v>
       </c>
       <c r="P83" s="3">
         <v>18300</v>
       </c>
       <c r="Q83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="R83" s="3">
         <v>18600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>18100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>15600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>14700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>14100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>11300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E89" s="3">
         <v>10200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>26300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>67700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>39100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>85700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>90900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>60100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>87200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>75300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>127900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>19200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>36600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>66600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>23800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>40600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
@@ -7933,97 +8154,100 @@
         <v>-10500</v>
       </c>
       <c r="E91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8300</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-10400</v>
       </c>
       <c r="AC91" s="3">
         <v>-10400</v>
       </c>
       <c r="AD91" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>113200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>647600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-349600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-55700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-182700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-330100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-54900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-50700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-68400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-240600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -8361,52 +8595,52 @@
         <v>-3200</v>
       </c>
       <c r="E96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F96" s="3">
         <v>-3100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3300</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-3200</v>
       </c>
       <c r="H96" s="3">
         <v>-3200</v>
       </c>
       <c r="I96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J96" s="3">
         <v>-3300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-3200</v>
       </c>
       <c r="U96" s="3">
         <v>-3200</v>
@@ -8415,28 +8649,28 @@
         <v>-3200</v>
       </c>
       <c r="W96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AE96" s="3">
         <v>-3200</v>
@@ -8445,13 +8679,16 @@
         <v>-3200</v>
       </c>
       <c r="AG96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="AH96" s="3">
         <v>-2900</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-2900</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8744,168 +8987,174 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-304900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>307900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>109800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-86100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-61100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-94500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>34300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-81000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>314000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>53700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-113500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>39300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>29900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>15500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>53500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>186900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-2900</v>
       </c>
       <c r="K101" s="3">
         <v>-2900</v>
       </c>
       <c r="L101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>200</v>
       </c>
       <c r="X101" s="3">
         <v>200</v>
@@ -8914,128 +9163,134 @@
         <v>200</v>
       </c>
       <c r="Z101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>81600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>357000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-144100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>144800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>JBT</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>453800</v>
+      </c>
+      <c r="E8" s="3">
         <v>402300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>392300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>444600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>403600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>427700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>388500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>441200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>398800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>394000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>356300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>497600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>477400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>475500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>417800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>439400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>419200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>411500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>457700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>545500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>489400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>493300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>417500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>537300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>481900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>491300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>409200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>483700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>420800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>386100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>344500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>405000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>349600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>290200</v>
+      </c>
+      <c r="E9" s="3">
         <v>259100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>252000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>281100</v>
       </c>
-      <c r="G9" s="3">
-        <v>259700</v>
-      </c>
       <c r="H9" s="3">
-        <v>304900</v>
+        <v>258800</v>
       </c>
       <c r="I9" s="3">
-        <v>512100</v>
+        <v>280500</v>
       </c>
       <c r="J9" s="3">
+        <v>255600</v>
+      </c>
+      <c r="K9" s="3">
         <v>295800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>263300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>265300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>236500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>356400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>334900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>325600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>284600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>306100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>292000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>281300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>311900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>379000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>340500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>337900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>289900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>379200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>346900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>351000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>305600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>346800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>299300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>270500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>247000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>969900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>255600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E10" s="3">
         <v>143200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>140300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>163500</v>
       </c>
-      <c r="G10" s="3">
-        <v>143900</v>
-      </c>
       <c r="H10" s="3">
-        <v>122800</v>
+        <v>144800</v>
       </c>
       <c r="I10" s="3">
-        <v>-123600</v>
+        <v>147200</v>
       </c>
       <c r="J10" s="3">
+        <v>132900</v>
+      </c>
+      <c r="K10" s="3">
         <v>145400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>135500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>128700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>119800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>141200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>142500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>149900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>133200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>133300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>127200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>130200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>145800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>166500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>148900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>155400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>127600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>158100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>135000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>140300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>103600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>136900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>121500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>115600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>97500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-564900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>94000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1167,8 @@
       <c r="F12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>91</v>
+      <c r="G12" s="3">
+        <v>20500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>91</v>
@@ -1210,38 +1224,41 @@
       <c r="Y12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA12" s="3">
         <v>6200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,132 +1358,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
+        <v>12700</v>
       </c>
       <c r="E14" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G14" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M14" s="3">
+        <v>800</v>
+      </c>
+      <c r="N14" s="3">
+        <v>600</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P14" s="3">
         <v>1100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>800</v>
-      </c>
-      <c r="J14" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L14" s="3">
-        <v>800</v>
-      </c>
-      <c r="M14" s="3">
-        <v>600</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2500</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1000</v>
       </c>
       <c r="Q14" s="3">
         <v>1000</v>
       </c>
       <c r="R14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2100</v>
-      </c>
-      <c r="U14" s="3">
-        <v>2000</v>
       </c>
       <c r="V14" s="3">
         <v>2000</v>
       </c>
       <c r="W14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>11600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>8500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>22200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>22200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>22100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>23100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>22700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>375500</v>
+        <v>395300</v>
       </c>
       <c r="E17" s="3">
-        <v>363200</v>
+        <v>361800</v>
       </c>
       <c r="F17" s="3">
-        <v>386800</v>
+        <v>357900</v>
       </c>
       <c r="G17" s="3">
-        <v>367600</v>
+        <v>379200</v>
       </c>
       <c r="H17" s="3">
-        <v>383400</v>
+        <v>360500</v>
       </c>
       <c r="I17" s="3">
-        <v>360100</v>
+        <v>380000</v>
       </c>
       <c r="J17" s="3">
+        <v>357000</v>
+      </c>
+      <c r="K17" s="3">
         <v>398400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>364000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>362000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>333300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>463100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>436900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>428200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>380000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>395900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>390900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>363900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>414000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>482900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>440800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>446300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>387500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>478200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>445300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>449100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>403300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>430300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>378600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>356400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>324000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>370700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>320100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>26800</v>
+        <v>58500</v>
       </c>
       <c r="E18" s="3">
-        <v>29100</v>
+        <v>40500</v>
       </c>
       <c r="F18" s="3">
-        <v>57800</v>
+        <v>34400</v>
       </c>
       <c r="G18" s="3">
-        <v>36000</v>
+        <v>65400</v>
       </c>
       <c r="H18" s="3">
-        <v>44300</v>
+        <v>43100</v>
       </c>
       <c r="I18" s="3">
-        <v>28400</v>
+        <v>47700</v>
       </c>
       <c r="J18" s="3">
+        <v>31500</v>
+      </c>
+      <c r="K18" s="3">
         <v>42800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>47300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>43500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>28300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>62600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>48600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>47000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>59100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>36600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>42200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>53400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>42200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>29700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>20500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>34300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,61 +1849,62 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>4700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>4700</v>
+      <c r="D20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F20" s="3">
-        <v>13100</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>-300</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>800</v>
-      </c>
-      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="3">
         <v>3800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-1000</v>
       </c>
       <c r="U20" s="3">
         <v>-1000</v>
@@ -1879,7 +1913,7 @@
         <v>-1000</v>
       </c>
       <c r="W20" s="3">
-        <v>-500</v>
+        <v>-1000</v>
       </c>
       <c r="X20" s="3">
         <v>-500</v>
@@ -1888,20 +1922,20 @@
         <v>-500</v>
       </c>
       <c r="Z20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1912,114 +1946,120 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>53700</v>
+        <v>80700</v>
       </c>
       <c r="E21" s="3">
+        <v>62700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>56400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>72800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>66100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>71200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>54200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>67400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>53500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>48700</v>
+      </c>
+      <c r="N21" s="3">
+        <v>42900</v>
+      </c>
+      <c r="O21" s="3">
+        <v>56100</v>
+      </c>
+      <c r="P21" s="3">
+        <v>60400</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>65600</v>
+      </c>
+      <c r="R21" s="3">
+        <v>56100</v>
+      </c>
+      <c r="S21" s="3">
+        <v>61500</v>
+      </c>
+      <c r="T21" s="3">
+        <v>45200</v>
+      </c>
+      <c r="U21" s="3">
+        <v>64300</v>
+      </c>
+      <c r="V21" s="3">
+        <v>60200</v>
+      </c>
+      <c r="W21" s="3">
+        <v>79700</v>
+      </c>
+      <c r="X21" s="3">
+        <v>65300</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>62100</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>44200</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>73400</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>51900</v>
+      </c>
+      <c r="AC21" s="3">
         <v>55900</v>
       </c>
-      <c r="F21" s="3">
-        <v>92900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>58800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>68700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>51900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>67400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>53500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>48700</v>
-      </c>
-      <c r="M21" s="3">
-        <v>42900</v>
-      </c>
-      <c r="N21" s="3">
-        <v>56100</v>
-      </c>
-      <c r="O21" s="3">
-        <v>60400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>65600</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>56100</v>
-      </c>
-      <c r="R21" s="3">
-        <v>61500</v>
-      </c>
-      <c r="S21" s="3">
-        <v>45200</v>
-      </c>
-      <c r="T21" s="3">
-        <v>64300</v>
-      </c>
-      <c r="U21" s="3">
-        <v>60200</v>
-      </c>
-      <c r="V21" s="3">
-        <v>79700</v>
-      </c>
-      <c r="W21" s="3">
-        <v>65300</v>
-      </c>
-      <c r="X21" s="3">
-        <v>62100</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>44200</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>73400</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>51900</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>55900</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>19400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>67200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>55000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>42600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>32700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>46200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2027,37 +2067,37 @@
         <v>4100</v>
       </c>
       <c r="E22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9800</v>
       </c>
-      <c r="G22" s="3">
-        <v>900</v>
-      </c>
       <c r="H22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I22" s="3">
         <v>8200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>2100</v>
       </c>
       <c r="P22" s="3">
         <v>2100</v>
@@ -2066,31 +2106,31 @@
         <v>2100</v>
       </c>
       <c r="R22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S22" s="3">
         <v>2700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3300</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>3400</v>
       </c>
       <c r="AA22" s="3">
         <v>3400</v>
@@ -2099,230 +2139,239 @@
         <v>3400</v>
       </c>
       <c r="AC22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E23" s="3">
         <v>27400</v>
       </c>
-      <c r="E23" s="3">
-        <v>30900</v>
-      </c>
       <c r="F23" s="3">
+        <v>30800</v>
+      </c>
+      <c r="G23" s="3">
         <v>61100</v>
       </c>
-      <c r="G23" s="3">
-        <v>34800</v>
-      </c>
       <c r="H23" s="3">
+        <v>35700</v>
+      </c>
+      <c r="I23" s="3">
         <v>37000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>45200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>40200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>43100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>37900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>56200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>42200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>42300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>55400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>33200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>38400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>50100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>38600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>26400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>31900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>26700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6400</v>
       </c>
-      <c r="G24" s="3">
-        <v>4300</v>
-      </c>
       <c r="H24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I24" s="3">
         <v>8600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>8500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E26" s="3">
         <v>30700</v>
       </c>
-      <c r="E26" s="3">
-        <v>22800</v>
-      </c>
       <c r="F26" s="3">
+        <v>22700</v>
+      </c>
+      <c r="G26" s="3">
         <v>54700</v>
       </c>
-      <c r="G26" s="3">
-        <v>30500</v>
-      </c>
       <c r="H26" s="3">
+        <v>31100</v>
+      </c>
+      <c r="I26" s="3">
         <v>28400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>25700</v>
       </c>
       <c r="L26" s="3">
         <v>25700</v>
       </c>
       <c r="M26" s="3">
+        <v>25700</v>
+      </c>
+      <c r="N26" s="3">
         <v>19900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>31600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>32500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>42100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>33500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>34000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>41800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>33500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>35300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>26400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>17600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E27" s="3">
         <v>30700</v>
       </c>
-      <c r="E27" s="3">
-        <v>22700</v>
-      </c>
       <c r="F27" s="3">
-        <v>54700</v>
+        <v>22800</v>
       </c>
       <c r="G27" s="3">
-        <v>30500</v>
+        <v>58400</v>
       </c>
       <c r="H27" s="3">
-        <v>28400</v>
+        <v>441600</v>
       </c>
       <c r="I27" s="3">
-        <v>17100</v>
+        <v>32700</v>
       </c>
       <c r="J27" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K27" s="3">
         <v>32500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>25700</v>
       </c>
       <c r="L27" s="3">
         <v>25700</v>
       </c>
       <c r="M27" s="3">
+        <v>25700</v>
+      </c>
+      <c r="N27" s="3">
         <v>19900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>32500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>42100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>33500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>34000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>41800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>33500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>35300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>26400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>18300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>17600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2725,44 +2783,47 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>3700</v>
       </c>
-      <c r="G29" s="3">
-        <v>437100</v>
-      </c>
       <c r="H29" s="3">
-        <v>7600</v>
+        <v>410500</v>
       </c>
       <c r="I29" s="3">
-        <v>19300</v>
+        <v>4300</v>
       </c>
       <c r="J29" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K29" s="3">
         <v>11700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>8500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>7700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>5700</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -2791,43 +2852,46 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-300</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-15900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3028,61 +3095,64 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-4700</v>
+      <c r="D32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F32" s="3">
-        <v>-13100</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1000</v>
       </c>
       <c r="U32" s="3">
         <v>1000</v>
@@ -3091,7 +3161,7 @@
         <v>1000</v>
       </c>
       <c r="W32" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="X32" s="3">
         <v>500</v>
@@ -3100,20 +3170,20 @@
         <v>500</v>
       </c>
       <c r="Z32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3124,114 +3194,120 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E33" s="3">
         <v>30700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58400</v>
       </c>
-      <c r="G33" s="3">
-        <v>467600</v>
-      </c>
       <c r="H33" s="3">
-        <v>36000</v>
+        <v>441600</v>
       </c>
       <c r="I33" s="3">
-        <v>36400</v>
+        <v>32700</v>
       </c>
       <c r="J33" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K33" s="3">
         <v>44200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>33400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>17200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>32500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>42100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>33500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>33700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>42900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>33600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>19400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>25800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E35" s="3">
         <v>30700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58400</v>
       </c>
-      <c r="G35" s="3">
-        <v>467600</v>
-      </c>
       <c r="H35" s="3">
-        <v>36000</v>
+        <v>441600</v>
       </c>
       <c r="I35" s="3">
-        <v>36400</v>
+        <v>32700</v>
       </c>
       <c r="J35" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K35" s="3">
         <v>44200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>33400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>17200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>32500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>42100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>33500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>33700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>42900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>33600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>19400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>25800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>534500</v>
+      </c>
+      <c r="E41" s="3">
         <v>474300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>479000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>483300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>401700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>58200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>202300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>47500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>50600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>58000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>75400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>39100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>43000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>36300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>34000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>38400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>26300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>42900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>91</v>
+      <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>600</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>125000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>91</v>
+      <c r="I42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>91</v>
@@ -3748,8 +3838,8 @@
       <c r="M42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3814,435 +3904,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>334600</v>
+      </c>
+      <c r="E43" s="3">
         <v>311500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>299300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>288900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>259900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>279600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>383800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>265600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>374100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>366600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>340900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>333500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>319700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>307100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>281500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>304400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>305000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>302600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>338700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>363300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>354700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>357300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>295800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>323700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>334000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>318700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>287600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>316400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>299900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>281800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>246600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>260500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>240900</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E44" s="3">
         <v>258700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>250200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>238900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>226700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>237200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>351900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>202000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>346800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>298800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>275600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>229100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>217900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>204100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>195700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>197300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>219700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>229100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>237200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>245000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>264000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>260400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>226400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>206100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>256600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>270500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>305400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>190200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>217500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>198300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>178400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>139600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>80900</v>
+        <v>76500</v>
       </c>
       <c r="E45" s="3">
-        <v>73900</v>
+        <v>79900</v>
       </c>
       <c r="F45" s="3">
+        <v>73300</v>
+      </c>
+      <c r="G45" s="3">
         <v>89100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>78300</v>
       </c>
-      <c r="H45" s="3">
-        <v>327200</v>
-      </c>
       <c r="I45" s="3">
+        <v>324700</v>
+      </c>
+      <c r="J45" s="3">
         <v>84800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>325200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>73400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>76400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>77300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>68600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>64600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>62700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>66900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>59200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>50500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>51700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>60400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>57300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>58600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>60700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>45700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>57600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>59700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>55000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>48000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>53500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>54000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>52600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>51700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>40200</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1205600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1125400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1102400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1100200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1091600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>886800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>866200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>926500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>874400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>806900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>777100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>718700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>664400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>778100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>597400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>616100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>634500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>640200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>703000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>708200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>725100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>715400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>626800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>618500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>686700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>685200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>678600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>588600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>609300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>560400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>520500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>485000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>472400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+        <v>11700</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>243300</v>
+      </c>
+      <c r="E48" s="3">
         <v>242000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>246700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>248000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>245100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>246600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>273100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>245400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>262200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>263400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>269200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>267600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>268300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>267800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>263300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>268000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>261900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>262200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>261300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>265600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>264500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>265400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>237500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>239700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>238900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>234800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>242900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>233000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>231000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>220700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>216800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>210200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>187600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1144600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1139000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1151200</v>
       </c>
-      <c r="F49" s="3">
-        <v>1168400</v>
-      </c>
       <c r="G49" s="3">
+        <v>1237500</v>
+      </c>
+      <c r="H49" s="3">
         <v>1166200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1186400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1249700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1200200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1236000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>976600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1011000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1027400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>999400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>841300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>846600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>843000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>832900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>828000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>831200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>854800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>842800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>856600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>576500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>535300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>543000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>508900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>524100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>518600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>522300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>479900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>474900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>425500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>183700</v>
+        <v>182400</v>
       </c>
       <c r="E52" s="3">
-        <v>190400</v>
+        <v>171300</v>
       </c>
       <c r="F52" s="3">
-        <v>193800</v>
+        <v>178700</v>
       </c>
       <c r="G52" s="3">
-        <v>185900</v>
+        <v>102500</v>
       </c>
       <c r="H52" s="3">
-        <v>268000</v>
+        <v>173800</v>
       </c>
       <c r="I52" s="3">
-        <v>190600</v>
+        <v>259300</v>
       </c>
       <c r="J52" s="3">
+        <v>177700</v>
+      </c>
+      <c r="K52" s="3">
         <v>268900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>181900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>175200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>152600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>127700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>106400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>89100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>87000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>82600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>90600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>88700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>86300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>86400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>74900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>80800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>49000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>52600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>50200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>52400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>51200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>62300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>58600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>59600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>66700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>2789000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2690100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2690700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2710400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2688800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2587800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2579600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2641000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2554500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2222100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2209900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2141400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2038500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1976300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1794300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1805900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1811900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1821000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1884200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1914900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1918800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1912300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1521600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1442500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1521200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1479100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1498000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1391400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1424900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1319600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1271800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1187400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>960700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E57" s="3">
         <v>135600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>142400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>134600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>121300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>137400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>215300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>170600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>221000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>222900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>212500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>186000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>183400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>177900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>150000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>140700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>152000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>150400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>159200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>198600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>186800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>189100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>154800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>191200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>174100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>162100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>156800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>157100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>159100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>139400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>137300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>135700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>120700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>800</v>
+      </c>
+      <c r="K58" s="3">
+        <v>600</v>
+      </c>
+      <c r="L58" s="3">
+        <v>800</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="N58" s="3">
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>600</v>
+      </c>
+      <c r="R58" s="3">
+        <v>500</v>
+      </c>
+      <c r="S58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T58" s="3">
+        <v>200</v>
+      </c>
+      <c r="U58" s="3">
+        <v>100</v>
+      </c>
+      <c r="V58" s="3">
+        <v>300</v>
+      </c>
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
-        <v>800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>800</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="M58" s="3">
-        <v>100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>300</v>
-      </c>
-      <c r="P58" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="X58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>500</v>
-      </c>
-      <c r="R58" s="3">
-        <v>2400</v>
-      </c>
-      <c r="S58" s="3">
-        <v>200</v>
-      </c>
-      <c r="T58" s="3">
-        <v>100</v>
-      </c>
-      <c r="U58" s="3">
-        <v>300</v>
-      </c>
-      <c r="V58" s="3">
-        <v>900</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="X58" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>100</v>
       </c>
       <c r="AB58" s="3">
         <v>100</v>
       </c>
       <c r="AC58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD58" s="3">
         <v>8900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>307300</v>
+        <v>283500</v>
       </c>
       <c r="E59" s="3">
-        <v>323700</v>
+        <v>266300</v>
       </c>
       <c r="F59" s="3">
-        <v>349800</v>
+        <v>290500</v>
       </c>
       <c r="G59" s="3">
+        <v>275400</v>
+      </c>
+      <c r="H59" s="3">
         <v>463000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>471700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>402200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>452800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>397400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>383800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>383300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>363900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>319100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>300400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>318900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>314400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>282400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>261800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>252600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>275000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>284400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>292000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>298700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>293600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>322200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>353900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>378000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>273800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>304000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>256700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>257100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>250200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>473400</v>
+      </c>
+      <c r="E60" s="3">
         <v>442900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>466100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>484400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>584300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>610000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>618300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>624000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>619200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>606700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>595900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>549900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>502800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>478900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>469400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>457500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>434600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>412300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>412100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>474500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>472800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>484000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>453500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>485300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>496400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>516100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>543700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>441400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>475300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>403700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>402200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>393000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>390500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>651500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>650900</v>
+      </c>
+      <c r="F61" s="3">
+        <v>650500</v>
+      </c>
+      <c r="G61" s="3">
+        <v>675000</v>
+      </c>
+      <c r="H61" s="3">
+        <v>645800</v>
+      </c>
+      <c r="I61" s="3">
+        <v>949600</v>
+      </c>
+      <c r="J61" s="3">
+        <v>956500</v>
+      </c>
+      <c r="K61" s="3">
+        <v>977300</v>
+      </c>
+      <c r="L61" s="3">
+        <v>979000</v>
+      </c>
+      <c r="M61" s="3">
+        <v>674600</v>
+      </c>
+      <c r="N61" s="3">
+        <v>669900</v>
+      </c>
+      <c r="O61" s="3">
+        <v>674400</v>
+      </c>
+      <c r="P61" s="3">
+        <v>652900</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>641100</v>
+      </c>
+      <c r="R61" s="3">
+        <v>469300</v>
+      </c>
+      <c r="S61" s="3">
+        <v>522500</v>
+      </c>
+      <c r="T61" s="3">
+        <v>598000</v>
+      </c>
+      <c r="U61" s="3">
         <v>647600</v>
       </c>
-      <c r="E61" s="3">
-        <v>647000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>646400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>645800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>949600</v>
-      </c>
-      <c r="I61" s="3">
-        <v>956500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>977300</v>
-      </c>
-      <c r="K61" s="3">
-        <v>979000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>674600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>669900</v>
-      </c>
-      <c r="N61" s="3">
-        <v>674400</v>
-      </c>
-      <c r="O61" s="3">
-        <v>652900</v>
-      </c>
-      <c r="P61" s="3">
-        <v>641100</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>469300</v>
-      </c>
-      <c r="R61" s="3">
-        <v>522500</v>
-      </c>
-      <c r="S61" s="3">
-        <v>598000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>647600</v>
-      </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>733600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>698300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>768700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>771500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>448200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>387100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>486100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>437200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>407400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>372700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>391800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>391900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>372600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>491600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>300200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>80800</v>
+        <v>56600</v>
       </c>
       <c r="E62" s="3">
-        <v>86500</v>
+        <v>55500</v>
       </c>
       <c r="F62" s="3">
-        <v>90700</v>
+        <v>59700</v>
       </c>
       <c r="G62" s="3">
-        <v>85600</v>
+        <v>37500</v>
       </c>
       <c r="H62" s="3">
-        <v>107000</v>
+        <v>67300</v>
       </c>
       <c r="I62" s="3">
-        <v>113800</v>
+        <v>78300</v>
       </c>
       <c r="J62" s="3">
+        <v>82400</v>
+      </c>
+      <c r="K62" s="3">
         <v>134300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>150100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>151000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>160500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>166600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>175500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>170600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>183500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>188800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>167900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>164500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>167800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>172600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>153600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>156800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>143500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>113200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>106300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>115200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>127900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>135400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>127500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>121300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>120700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>122900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>1203900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1171300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1199600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1221500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1315700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1666600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1688600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1735600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1748300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1432300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1426300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1390900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1331200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1290600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1122200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1168800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1200500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1224400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1313500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1345400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1395100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1412300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1045200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>985600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1088800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1068500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1079000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>949500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>994600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>916900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>895500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1007500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>791600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>1546300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1510600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1483100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1463600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1365600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>901500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>873700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>894000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>817000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>786000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>755800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>733400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>705000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>678900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>651600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>627800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>600900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>586900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>557600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>532800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>493900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>463700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>433100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>416500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>354700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>333800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>303400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>333700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>317600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>295000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>280300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>266600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1585100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1518800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1491100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1488900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1373100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>921200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>891000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>905400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>806200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>789800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>783600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>750500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>707300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>685700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>672100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>637100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>611400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>596600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>570700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>569500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>523700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>500000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>476400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>456900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>432400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>410600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>419000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>441900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>430300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>402700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>376300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>179900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E81" s="3">
         <v>30700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58400</v>
       </c>
-      <c r="G81" s="3">
-        <v>467600</v>
-      </c>
       <c r="H81" s="3">
-        <v>36000</v>
+        <v>441600</v>
       </c>
       <c r="I81" s="3">
-        <v>36400</v>
+        <v>32700</v>
       </c>
       <c r="J81" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K81" s="3">
         <v>44200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>33400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>17200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>32500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>42100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>33500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>33700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>42900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>33600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>19400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>25800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>22200</v>
+        <v>23100</v>
       </c>
       <c r="E83" s="3">
-        <v>22100</v>
+        <v>23500</v>
       </c>
       <c r="F83" s="3">
-        <v>22000</v>
+        <v>22700</v>
       </c>
       <c r="G83" s="3">
-        <v>23100</v>
+        <v>16300</v>
       </c>
       <c r="H83" s="3">
-        <v>22300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>23900</v>
+        <v>18800</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J83" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K83" s="3">
         <v>21900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>18300</v>
       </c>
       <c r="Q83" s="3">
         <v>18300</v>
       </c>
       <c r="R83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="S83" s="3">
         <v>18600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>18100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>14100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E89" s="3">
         <v>21700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10200</v>
       </c>
-      <c r="F89" s="3">
-        <v>-24600</v>
-      </c>
       <c r="G89" s="3">
-        <v>16300</v>
+        <v>-28000</v>
       </c>
       <c r="H89" s="3">
-        <v>26300</v>
+        <v>19700</v>
       </c>
       <c r="I89" s="3">
-        <v>21600</v>
+        <v>29700</v>
       </c>
       <c r="J89" s="3">
+        <v>18200</v>
+      </c>
+      <c r="K89" s="3">
         <v>67700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>39100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>62400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>33000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>85700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>90900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>60100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>87200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>75300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>127900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>19200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>66600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>23800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>40600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-10500</v>
+        <v>-6900</v>
       </c>
       <c r="E91" s="3">
         <v>-10500</v>
       </c>
       <c r="F91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-8900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8300</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-10400</v>
       </c>
       <c r="AD91" s="3">
         <v>-10400</v>
       </c>
       <c r="AE91" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
-        <v>113200</v>
-      </c>
       <c r="G94" s="3">
-        <v>647600</v>
+        <v>116600</v>
       </c>
       <c r="H94" s="3">
+        <v>644200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-17600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-349600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-55700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-182700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-330100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-54900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-68400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-240600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8586,64 +8819,65 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F96" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G96" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H96" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I96" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J96" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="M96" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N96" s="3">
         <v>-3200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="O96" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="Q96" s="3">
         <v>-3100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="R96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="S96" s="3">
         <v>-3300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="T96" s="3">
         <v>-3200</v>
       </c>
-      <c r="I96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="U96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-3200</v>
       </c>
       <c r="V96" s="3">
         <v>-3200</v>
@@ -8652,28 +8886,28 @@
         <v>-3200</v>
       </c>
       <c r="X96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-3200</v>
       </c>
       <c r="AF96" s="3">
         <v>-3200</v>
@@ -8682,13 +8916,16 @@
         <v>-3200</v>
       </c>
       <c r="AH96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="AI96" s="3">
         <v>-2900</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-2900</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8990,174 +9233,180 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-304900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>307900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>109800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-50000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-86100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-61100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-94500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>34300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-81000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>314000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>53700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-113500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>39300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>29900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>15500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>53500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>186900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-600</v>
+        <v>-2000</v>
       </c>
       <c r="E101" s="3">
-        <v>-1200</v>
+        <v>-500</v>
       </c>
       <c r="F101" s="3">
-        <v>1400</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>-2000</v>
+        <v>2400</v>
       </c>
       <c r="H101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
+        <v>-2900</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J101" s="3">
+        <v>900</v>
+      </c>
+      <c r="K101" s="3">
         <v>2400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-2900</v>
       </c>
       <c r="L101" s="3">
         <v>-2900</v>
       </c>
       <c r="M101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1400</v>
-      </c>
-      <c r="X101" s="3">
-        <v>200</v>
       </c>
       <c r="Y101" s="3">
         <v>200</v>
@@ -9166,131 +9415,137 @@
         <v>200</v>
       </c>
       <c r="AA101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>81600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>357000</v>
       </c>
-      <c r="H102" s="3">
-        <v>-1000</v>
-      </c>
       <c r="I102" s="3">
-        <v>-27400</v>
+        <v>800</v>
       </c>
       <c r="J102" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="K102" s="3">
         <v>20500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-144100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>144800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>12800</v>
       </c>
     </row>
